--- a/artfynd/A 61804-2023 artfynd.xlsx
+++ b/artfynd/A 61804-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61804-2023 artfynd.xlsx
+++ b/artfynd/A 61804-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 61804-2023 artfynd.xlsx
+++ b/artfynd/A 61804-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92405316</v>
+        <v>92405382</v>
       </c>
       <c r="B2" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102020</v>
+        <v>102018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584738.0473999321</v>
+        <v>584738</v>
       </c>
       <c r="R2" t="n">
-        <v>6403363.900812932</v>
+        <v>6403364</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,19 +756,9 @@
           <t>2020-07-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92405382</v>
+        <v>92405316</v>
       </c>
       <c r="B3" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102018</v>
+        <v>102020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584738.0473999321</v>
+        <v>584738</v>
       </c>
       <c r="R3" t="n">
-        <v>6403363.900812932</v>
+        <v>6403364</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,19 +867,9 @@
           <t>2020-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,6 +894,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>92405456</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dröppshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584783</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6403398</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Wallberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Wallberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
